--- a/output_phyto/phyto_Intermediate_badger_2013b.xlsx
+++ b/output_phyto/phyto_Intermediate_badger_2013b.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="301">
   <si>
     <t>NA</t>
   </si>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">10.1002/palo.20015</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/phytoplankton_badger_2013b.xlsx</t>
+    <t xml:space="preserve">phytoplankton_badger_2013b_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">Mk37_2</t>
   </si>
   <si>
-    <t xml:space="preserve">MgCa_G_trilobus</t>
+    <t xml:space="preserve">average of published Uk37 and MgCa temperatures</t>
   </si>
   <si>
     <t xml:space="preserve">No phosphate reported, but they do state a b-value. Depths were estimated from linear interpolation of age and depth. Epsilon_p uncertainty in the PANGAEA spreadsheet is assumed to be 2std, because the paper typically states uncertainties are 2std, and they are quite large to be 1std.</t>
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">phytoplankton_Badger_2013b_5</t>
   </si>
   <si>
-    <t xml:space="preserve">interpolated between samples</t>
+    <t xml:space="preserve">published temperature</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Badger_2013b_6</t>
@@ -1536,6 +1536,9 @@
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Badger_2013b_19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">published Uk37 temperature</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Badger_2013b_20</t>
@@ -1549,7 +1552,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1615,12 +1618,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1734,7 +1731,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1833,7 +1830,6 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2559,7 +2555,7 @@
       <c r="B5" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" t="s">
         <v>272</v>
       </c>
       <c r="D5" t="s">
@@ -2577,8 +2573,8 @@
       <c r="H5" t="n">
         <v>13.799</v>
       </c>
-      <c r="I5" t="e">
-        <v>#N/A</v>
+      <c r="I5" t="n">
+        <v>0.0699007121843967</v>
       </c>
       <c r="J5" t="e">
         <v>#N/A</v>
@@ -2596,7 +2592,7 @@
         <v>-21.39</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P5" t="e">
         <v>#N/A</v>
@@ -2605,10 +2601,10 @@
         <v>#N/A</v>
       </c>
       <c r="R5" s="11" t="n">
-        <v>33.5</v>
+        <v>31.25</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>2.343074902772</v>
       </c>
       <c r="T5" t="e">
         <v>#N/A</v>
@@ -2634,20 +2630,20 @@
       <c r="AA5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB5" t="e">
-        <v>#N/A</v>
+      <c r="AB5" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF5" t="e">
-        <v>#N/A</v>
+      <c r="AD5" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG5" t="e">
         <v>#N/A</v>
@@ -2669,7 +2665,7 @@
       <c r="B6" t="s">
         <v>271</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" t="s">
         <v>272</v>
       </c>
       <c r="D6" t="s">
@@ -2687,8 +2683,8 @@
       <c r="H6" t="n">
         <v>13.792</v>
       </c>
-      <c r="I6" t="e">
-        <v>#N/A</v>
+      <c r="I6" t="n">
+        <v>0.0698670890896852</v>
       </c>
       <c r="J6" t="e">
         <v>#N/A</v>
@@ -2706,7 +2702,7 @@
         <v>-21.14</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P6" t="e">
         <v>#N/A</v>
@@ -2715,10 +2711,10 @@
         <v>#N/A</v>
       </c>
       <c r="R6" s="11" t="n">
-        <v>32.04</v>
+        <v>30.52</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>2.343074902772</v>
       </c>
       <c r="T6" t="e">
         <v>#N/A</v>
@@ -2744,20 +2740,20 @@
       <c r="AA6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB6" t="e">
-        <v>#N/A</v>
+      <c r="AB6" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF6" t="e">
-        <v>#N/A</v>
+      <c r="AD6" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG6" t="e">
         <v>#N/A</v>
@@ -2779,7 +2775,7 @@
       <c r="B7" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" t="s">
         <v>272</v>
       </c>
       <c r="D7" t="s">
@@ -2797,8 +2793,8 @@
       <c r="H7" t="n">
         <v>13.786</v>
       </c>
-      <c r="I7" t="e">
-        <v>#N/A</v>
+      <c r="I7" t="n">
+        <v>0.0698382685906577</v>
       </c>
       <c r="J7" t="e">
         <v>#N/A</v>
@@ -2816,7 +2812,7 @@
         <v>-21.03</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P7" t="e">
         <v>#N/A</v>
@@ -2825,10 +2821,10 @@
         <v>#N/A</v>
       </c>
       <c r="R7" s="11" t="n">
-        <v>30.57</v>
+        <v>29.785</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>2.343074902772</v>
       </c>
       <c r="T7" t="e">
         <v>#N/A</v>
@@ -2854,20 +2850,20 @@
       <c r="AA7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB7" t="e">
-        <v>#N/A</v>
+      <c r="AB7" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF7" t="e">
-        <v>#N/A</v>
+      <c r="AD7" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG7" t="e">
         <v>#N/A</v>
@@ -2889,7 +2885,7 @@
       <c r="B8" t="s">
         <v>271</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" t="s">
         <v>272</v>
       </c>
       <c r="D8" t="s">
@@ -2907,8 +2903,8 @@
       <c r="H8" t="n">
         <v>13.779</v>
       </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
+      <c r="I8" t="n">
+        <v>0.0698046438538875</v>
       </c>
       <c r="J8" t="e">
         <v>#N/A</v>
@@ -2926,7 +2922,7 @@
         <v>-21.47</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P8" t="e">
         <v>#N/A</v>
@@ -2935,10 +2931,10 @@
         <v>#N/A</v>
       </c>
       <c r="R8" s="11" t="n">
-        <v>30.86</v>
+        <v>29.93</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>2.343074902772</v>
       </c>
       <c r="T8" t="e">
         <v>#N/A</v>
@@ -2964,20 +2960,20 @@
       <c r="AA8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB8" t="e">
-        <v>#N/A</v>
+      <c r="AB8" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF8" t="e">
-        <v>#N/A</v>
+      <c r="AD8" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG8" t="e">
         <v>#N/A</v>
@@ -2999,7 +2995,7 @@
       <c r="B9" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" t="s">
         <v>272</v>
       </c>
       <c r="D9" t="s">
@@ -3017,8 +3013,8 @@
       <c r="H9" t="n">
         <v>13.773</v>
       </c>
-      <c r="I9" t="e">
-        <v>#N/A</v>
+      <c r="I9" t="n">
+        <v>0.069775821946683</v>
       </c>
       <c r="J9" t="e">
         <v>#N/A</v>
@@ -3036,7 +3032,7 @@
         <v>-21.45</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P9" t="e">
         <v>#N/A</v>
@@ -3048,7 +3044,7 @@
         <v>31.13</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="T9" t="e">
         <v>#N/A</v>
@@ -3074,20 +3070,20 @@
       <c r="AA9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB9" t="e">
-        <v>#N/A</v>
+      <c r="AB9" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF9" t="e">
-        <v>#N/A</v>
+      <c r="AD9" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG9" t="e">
         <v>#N/A</v>
@@ -3109,7 +3105,7 @@
       <c r="B10" t="s">
         <v>271</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" t="s">
         <v>272</v>
       </c>
       <c r="D10" t="s">
@@ -3127,8 +3123,8 @@
       <c r="H10" t="n">
         <v>13.766</v>
       </c>
-      <c r="I10" t="e">
-        <v>#N/A</v>
+      <c r="I10" t="n">
+        <v>0.0697421955662242</v>
       </c>
       <c r="J10" t="e">
         <v>#N/A</v>
@@ -3146,7 +3142,7 @@
         <v>-22.58</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P10" t="e">
         <v>#N/A</v>
@@ -3155,10 +3151,10 @@
         <v>#N/A</v>
       </c>
       <c r="R10" s="11" t="n">
-        <v>31.41</v>
+        <v>30.205</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>2.343074902772</v>
       </c>
       <c r="T10" t="e">
         <v>#N/A</v>
@@ -3184,20 +3180,20 @@
       <c r="AA10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB10" t="e">
-        <v>#N/A</v>
+      <c r="AB10" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF10" t="e">
-        <v>#N/A</v>
+      <c r="AD10" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG10" t="e">
         <v>#N/A</v>
@@ -3219,7 +3215,7 @@
       <c r="B11" t="s">
         <v>271</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" t="s">
         <v>272</v>
       </c>
       <c r="D11" t="s">
@@ -3237,8 +3233,8 @@
       <c r="H11" t="n">
         <v>13.76</v>
       </c>
-      <c r="I11" t="e">
-        <v>#N/A</v>
+      <c r="I11" t="n">
+        <v>0.0697133722494443</v>
       </c>
       <c r="J11" t="e">
         <v>#N/A</v>
@@ -3256,7 +3252,7 @@
         <v>-20.91</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P11" t="e">
         <v>#N/A</v>
@@ -3268,7 +3264,7 @@
         <v>30.01</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="T11" t="e">
         <v>#N/A</v>
@@ -3294,20 +3290,20 @@
       <c r="AA11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB11" t="e">
-        <v>#N/A</v>
+      <c r="AB11" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF11" t="e">
-        <v>#N/A</v>
+      <c r="AD11" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG11" t="e">
         <v>#N/A</v>
@@ -3329,7 +3325,7 @@
       <c r="B12" t="s">
         <v>271</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" t="s">
         <v>272</v>
       </c>
       <c r="D12" t="s">
@@ -3347,8 +3343,8 @@
       <c r="H12" t="n">
         <v>13.753</v>
       </c>
-      <c r="I12" t="e">
-        <v>#N/A</v>
+      <c r="I12" t="n">
+        <v>0.069679744223664</v>
       </c>
       <c r="J12" t="e">
         <v>#N/A</v>
@@ -3366,7 +3362,7 @@
         <v>-21.49</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P12" t="e">
         <v>#N/A</v>
@@ -3375,10 +3371,10 @@
         <v>#N/A</v>
       </c>
       <c r="R12" s="11" t="n">
-        <v>28.62</v>
+        <v>28.81</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>2.343074902772</v>
       </c>
       <c r="T12" t="e">
         <v>#N/A</v>
@@ -3404,20 +3400,20 @@
       <c r="AA12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB12" t="e">
-        <v>#N/A</v>
+      <c r="AB12" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF12" t="e">
-        <v>#N/A</v>
+      <c r="AD12" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG12" t="e">
         <v>#N/A</v>
@@ -3439,7 +3435,7 @@
       <c r="B13" t="s">
         <v>271</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" t="s">
         <v>272</v>
       </c>
       <c r="D13" t="s">
@@ -3457,8 +3453,8 @@
       <c r="H13" t="n">
         <v>13.741</v>
       </c>
-      <c r="I13" t="e">
-        <v>#N/A</v>
+      <c r="I13" t="n">
+        <v>0.0696220941164578</v>
       </c>
       <c r="J13" t="e">
         <v>#N/A</v>
@@ -3476,7 +3472,7 @@
         <v>-21.01</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P13" t="e">
         <v>#N/A</v>
@@ -3485,10 +3481,10 @@
         <v>#N/A</v>
       </c>
       <c r="R13" s="11" t="n">
-        <v>30.48</v>
+        <v>29.74</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>2.343074902772</v>
       </c>
       <c r="T13" t="e">
         <v>#N/A</v>
@@ -3514,20 +3510,20 @@
       <c r="AA13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB13" t="e">
-        <v>#N/A</v>
+      <c r="AB13" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF13" t="e">
-        <v>#N/A</v>
+      <c r="AD13" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG13" t="e">
         <v>#N/A</v>
@@ -3549,7 +3545,7 @@
       <c r="B14" t="s">
         <v>271</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" t="s">
         <v>272</v>
       </c>
       <c r="D14" t="s">
@@ -3567,8 +3563,8 @@
       <c r="H14" t="n">
         <v>13.716</v>
       </c>
-      <c r="I14" t="e">
-        <v>#N/A</v>
+      <c r="I14" t="n">
+        <v>0.0695019813473701</v>
       </c>
       <c r="J14" t="e">
         <v>#N/A</v>
@@ -3586,7 +3582,7 @@
         <v>-20.79</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P14" t="e">
         <v>#N/A</v>
@@ -3598,7 +3594,7 @@
         <v>30.3</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="T14" t="e">
         <v>#N/A</v>
@@ -3624,20 +3620,20 @@
       <c r="AA14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB14" t="e">
-        <v>#N/A</v>
+      <c r="AB14" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF14" t="e">
-        <v>#N/A</v>
+      <c r="AD14" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG14" t="e">
         <v>#N/A</v>
@@ -3659,7 +3655,7 @@
       <c r="B15" t="s">
         <v>271</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" t="s">
         <v>272</v>
       </c>
       <c r="D15" t="s">
@@ -3677,8 +3673,8 @@
       <c r="H15" t="n">
         <v>13.709</v>
       </c>
-      <c r="I15" t="e">
-        <v>#N/A</v>
+      <c r="I15" t="n">
+        <v>0.0694683477406496</v>
       </c>
       <c r="J15" t="e">
         <v>#N/A</v>
@@ -3696,7 +3692,7 @@
         <v>-21.02</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P15" t="e">
         <v>#N/A</v>
@@ -3705,10 +3701,10 @@
         <v>#N/A</v>
       </c>
       <c r="R15" s="11" t="n">
-        <v>30.43</v>
+        <v>28.315</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>2.343074902772</v>
       </c>
       <c r="T15" t="e">
         <v>#N/A</v>
@@ -3734,20 +3730,20 @@
       <c r="AA15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB15" t="e">
-        <v>#N/A</v>
+      <c r="AB15" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF15" t="e">
-        <v>#N/A</v>
+      <c r="AD15" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG15" t="e">
         <v>#N/A</v>
@@ -3769,7 +3765,7 @@
       <c r="B16" t="s">
         <v>271</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" t="s">
         <v>272</v>
       </c>
       <c r="D16" t="s">
@@ -3787,8 +3783,8 @@
       <c r="H16" t="n">
         <v>13.704</v>
       </c>
-      <c r="I16" t="e">
-        <v>#N/A</v>
+      <c r="I16" t="n">
+        <v>0.0694443231912159</v>
       </c>
       <c r="J16" t="e">
         <v>#N/A</v>
@@ -3806,7 +3802,7 @@
         <v>-20.31</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P16" t="e">
         <v>#N/A</v>
@@ -3815,10 +3811,10 @@
         <v>#N/A</v>
       </c>
       <c r="R16" s="11" t="n">
-        <v>29.03</v>
+        <v>28.765</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>2.343074902772</v>
       </c>
       <c r="T16" t="e">
         <v>#N/A</v>
@@ -3844,20 +3840,20 @@
       <c r="AA16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB16" t="e">
-        <v>#N/A</v>
+      <c r="AB16" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF16" t="e">
-        <v>#N/A</v>
+      <c r="AD16" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG16" t="e">
         <v>#N/A</v>
@@ -3879,7 +3875,7 @@
       <c r="B17" t="s">
         <v>271</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" t="s">
         <v>272</v>
       </c>
       <c r="D17" t="s">
@@ -3897,8 +3893,8 @@
       <c r="H17" t="n">
         <v>13.693</v>
       </c>
-      <c r="I17" t="e">
-        <v>#N/A</v>
+      <c r="I17" t="n">
+        <v>0.0693914675839306</v>
       </c>
       <c r="J17" t="e">
         <v>#N/A</v>
@@ -3916,7 +3912,7 @@
         <v>-20.87</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P17" t="e">
         <v>#N/A</v>
@@ -3928,7 +3924,7 @@
         <v>29.11</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="T17" t="e">
         <v>#N/A</v>
@@ -3954,20 +3950,20 @@
       <c r="AA17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB17" t="e">
-        <v>#N/A</v>
+      <c r="AB17" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF17" t="e">
-        <v>#N/A</v>
+      <c r="AD17" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG17" t="e">
         <v>#N/A</v>
@@ -3989,7 +3985,7 @@
       <c r="B18" t="s">
         <v>271</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" t="s">
         <v>272</v>
       </c>
       <c r="D18" t="s">
@@ -4007,8 +4003,8 @@
       <c r="H18" t="n">
         <v>13.679</v>
       </c>
-      <c r="I18" t="e">
-        <v>#N/A</v>
+      <c r="I18" t="n">
+        <v>0.0693241936296823</v>
       </c>
       <c r="J18" t="e">
         <v>#N/A</v>
@@ -4026,7 +4022,7 @@
         <v>-20.27</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P18" t="e">
         <v>#N/A</v>
@@ -4035,10 +4031,10 @@
         <v>#N/A</v>
       </c>
       <c r="R18" s="11" t="n">
-        <v>27.17</v>
+        <v>28.085</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>2.343074902772</v>
       </c>
       <c r="T18" t="e">
         <v>#N/A</v>
@@ -4064,20 +4060,20 @@
       <c r="AA18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB18" t="e">
-        <v>#N/A</v>
+      <c r="AB18" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF18" t="e">
-        <v>#N/A</v>
+      <c r="AD18" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG18" t="e">
         <v>#N/A</v>
@@ -4099,7 +4095,7 @@
       <c r="B19" t="s">
         <v>271</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" t="s">
         <v>272</v>
       </c>
       <c r="D19" t="s">
@@ -4117,8 +4113,8 @@
       <c r="H19" t="n">
         <v>13.672</v>
       </c>
-      <c r="I19" t="e">
-        <v>#N/A</v>
+      <c r="I19" t="n">
+        <v>0.0692905553152999</v>
       </c>
       <c r="J19" t="e">
         <v>#N/A</v>
@@ -4136,7 +4132,7 @@
         <v>-21.04</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P19" t="e">
         <v>#N/A</v>
@@ -4148,7 +4144,7 @@
         <v>27.98</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="T19" t="e">
         <v>#N/A</v>
@@ -4174,20 +4170,20 @@
       <c r="AA19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB19" t="e">
-        <v>#N/A</v>
+      <c r="AB19" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF19" t="e">
-        <v>#N/A</v>
+      <c r="AD19" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG19" t="e">
         <v>#N/A</v>
@@ -4209,7 +4205,7 @@
       <c r="B20" t="s">
         <v>271</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" t="s">
         <v>272</v>
       </c>
       <c r="D20" t="s">
@@ -4227,8 +4223,8 @@
       <c r="H20" t="n">
         <v>13.665</v>
       </c>
-      <c r="I20" t="e">
-        <v>#N/A</v>
+      <c r="I20" t="n">
+        <v>0.0692569161087718</v>
       </c>
       <c r="J20" t="e">
         <v>#N/A</v>
@@ -4246,7 +4242,7 @@
         <v>-21.27</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P20" t="e">
         <v>#N/A</v>
@@ -4255,10 +4251,10 @@
         <v>#N/A</v>
       </c>
       <c r="R20" s="11" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>2.343074902772</v>
       </c>
       <c r="T20" t="e">
         <v>#N/A</v>
@@ -4284,20 +4280,20 @@
       <c r="AA20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB20" t="e">
-        <v>#N/A</v>
+      <c r="AB20" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF20" t="e">
-        <v>#N/A</v>
+      <c r="AD20" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG20" t="e">
         <v>#N/A</v>
@@ -4319,7 +4315,7 @@
       <c r="B21" t="s">
         <v>271</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" t="s">
         <v>272</v>
       </c>
       <c r="D21" t="s">
@@ -4337,8 +4333,8 @@
       <c r="H21" t="n">
         <v>13.658</v>
       </c>
-      <c r="I21" t="e">
-        <v>#N/A</v>
+      <c r="I21" t="n">
+        <v>0.0692232760096174</v>
       </c>
       <c r="J21" t="e">
         <v>#N/A</v>
@@ -4356,7 +4352,7 @@
         <v>-21.37</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P21" t="e">
         <v>#N/A</v>
@@ -4365,10 +4361,10 @@
         <v>#N/A</v>
       </c>
       <c r="R21" s="11" t="n">
-        <v>29.04</v>
+        <v>29.02</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>2.343074902772</v>
       </c>
       <c r="T21" t="e">
         <v>#N/A</v>
@@ -4394,20 +4390,20 @@
       <c r="AA21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB21" t="e">
-        <v>#N/A</v>
+      <c r="AB21" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF21" t="e">
-        <v>#N/A</v>
+      <c r="AD21" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG21" t="e">
         <v>#N/A</v>
@@ -4429,7 +4425,7 @@
       <c r="B22" t="s">
         <v>271</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" t="s">
         <v>272</v>
       </c>
       <c r="D22" t="s">
@@ -4447,8 +4443,8 @@
       <c r="H22" t="n">
         <v>13.651</v>
       </c>
-      <c r="I22" t="e">
-        <v>#N/A</v>
+      <c r="I22" t="n">
+        <v>0.0691896350173554</v>
       </c>
       <c r="J22" t="e">
         <v>#N/A</v>
@@ -4466,7 +4462,7 @@
         <v>-20.85</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P22" t="e">
         <v>#N/A</v>
@@ -4475,10 +4471,10 @@
         <v>#N/A</v>
       </c>
       <c r="R22" s="11" t="n">
-        <v>28.97</v>
+        <v>28.985</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>2.343074902772</v>
       </c>
       <c r="T22" t="e">
         <v>#N/A</v>
@@ -4504,20 +4500,20 @@
       <c r="AA22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB22" t="e">
-        <v>#N/A</v>
+      <c r="AB22" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF22" t="e">
-        <v>#N/A</v>
+      <c r="AD22" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG22" t="e">
         <v>#N/A</v>
@@ -4539,7 +4535,7 @@
       <c r="B23" t="s">
         <v>271</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" t="s">
         <v>272</v>
       </c>
       <c r="D23" t="s">
@@ -4557,8 +4553,8 @@
       <c r="H23" t="n">
         <v>13.644</v>
       </c>
-      <c r="I23" t="e">
-        <v>#N/A</v>
+      <c r="I23" t="n">
+        <v>0.0691559931315043</v>
       </c>
       <c r="J23" t="e">
         <v>#N/A</v>
@@ -4576,7 +4572,7 @@
         <v>-21.12</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P23" t="e">
         <v>#N/A</v>
@@ -4585,10 +4581,10 @@
         <v>#N/A</v>
       </c>
       <c r="R23" s="11" t="n">
-        <v>28.97</v>
+        <v>29</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T23" t="e">
         <v>#N/A</v>
@@ -4597,7 +4593,7 @@
         <v>#N/A</v>
       </c>
       <c r="V23" s="11" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="W23" t="n">
         <v>0.25</v>
@@ -4614,20 +4610,20 @@
       <c r="AA23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB23" t="e">
-        <v>#N/A</v>
+      <c r="AB23" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF23" t="e">
-        <v>#N/A</v>
+      <c r="AD23" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG23" t="e">
         <v>#N/A</v>
@@ -4644,12 +4640,12 @@
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B24" t="s">
         <v>271</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" t="s">
         <v>272</v>
       </c>
       <c r="D24" t="s">
@@ -4667,8 +4663,8 @@
       <c r="H24" t="n">
         <v>13.602</v>
       </c>
-      <c r="I24" t="e">
-        <v>#N/A</v>
+      <c r="I24" t="n">
+        <v>0.0689541230239848</v>
       </c>
       <c r="J24" t="e">
         <v>#N/A</v>
@@ -4686,7 +4682,7 @@
         <v>-20.47</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P24" t="e">
         <v>#N/A</v>
@@ -4695,10 +4691,10 @@
         <v>#N/A</v>
       </c>
       <c r="R24" s="11" t="n">
-        <v>28.97</v>
+        <v>28.3</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T24" t="e">
         <v>#N/A</v>
@@ -4707,7 +4703,7 @@
         <v>#N/A</v>
       </c>
       <c r="V24" s="11" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="W24" t="n">
         <v>0.25</v>
@@ -4724,20 +4720,20 @@
       <c r="AA24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB24" t="e">
-        <v>#N/A</v>
+      <c r="AB24" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF24" t="e">
-        <v>#N/A</v>
+      <c r="AD24" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG24" t="e">
         <v>#N/A</v>
@@ -4754,12 +4750,12 @@
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B25" t="s">
         <v>271</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" t="s">
         <v>272</v>
       </c>
       <c r="D25" t="s">
@@ -4777,8 +4773,8 @@
       <c r="H25" t="n">
         <v>12.811</v>
       </c>
-      <c r="I25" t="e">
-        <v>#N/A</v>
+      <c r="I25" t="n">
+        <v>0.0651460851428914</v>
       </c>
       <c r="J25" t="e">
         <v>#N/A</v>
@@ -4796,7 +4792,7 @@
         <v>-21.68</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P25" t="e">
         <v>#N/A</v>
@@ -4805,10 +4801,10 @@
         <v>#N/A</v>
       </c>
       <c r="R25" s="11" t="n">
-        <v>27.62</v>
+        <v>28.6</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T25" t="e">
         <v>#N/A</v>
@@ -4817,7 +4813,7 @@
         <v>#N/A</v>
       </c>
       <c r="V25" s="11" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="W25" t="n">
         <v>0.25</v>
@@ -4834,20 +4830,20 @@
       <c r="AA25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB25" t="e">
-        <v>#N/A</v>
+      <c r="AB25" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF25" t="e">
-        <v>#N/A</v>
+      <c r="AD25" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG25" t="e">
         <v>#N/A</v>
@@ -5192,29 +5188,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
